--- a/任务表.xlsx
+++ b/任务表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="307">
   <si>
     <t>十周运维</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>《</t>
     </r>
     <r>
@@ -59,6 +65,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>《</t>
     </r>
     <r>
@@ -82,6 +94,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>《</t>
     </r>
     <r>
@@ -161,6 +179,12 @@
     <t>《docker》配套视频</t>
   </si>
   <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>逾期</t>
+  </si>
+  <si>
     <t>week 1-2 Linux系统基础</t>
   </si>
   <si>
@@ -1050,7 +1074,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1063,6 +1087,12 @@
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1246,12 +1276,36 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DD60C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DD60C"/>
+        <bgColor rgb="FF000000" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DD60C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1430,12 +1484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1818,137 +1866,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1958,58 +2006,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2021,7 +2063,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2033,7 +2075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2045,28 +2087,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2345,6 +2387,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="004DD60C"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2673,1261 +2720,1268 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:9">
-      <c r="A12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:9">
-      <c r="A13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="A13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="D13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" ht="28" spans="1:9">
-      <c r="A14" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="14" t="s">
+      <c r="A14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="D14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:9">
-      <c r="A15" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="A15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="D15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" ht="28" spans="1:9">
-      <c r="A16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="14" t="s">
+      <c r="A16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="C16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" ht="42" spans="1:6">
-      <c r="A17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" ht="28" spans="1:6">
+      <c r="A17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="C17" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" ht="42" spans="1:6">
-      <c r="A18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="D17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="E17" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" ht="28" spans="1:6">
+      <c r="A18" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" ht="42" spans="1:6">
-      <c r="A19" s="20" t="s">
+      <c r="D18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="E18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" ht="28" spans="1:6">
+      <c r="A19" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="B19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="C19" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" ht="42" spans="1:6">
-      <c r="A20" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="25" t="s">
+      <c r="D19" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="E19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" ht="28" spans="1:6">
+      <c r="A20" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="C20" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" ht="42" spans="1:6">
-      <c r="A21" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="25" t="s">
+      <c r="D20" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="E20" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" ht="28" spans="1:6">
+      <c r="A21" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="C21" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" ht="42" spans="1:6">
-      <c r="A22" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="D21" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="E21" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" ht="28" spans="1:6">
+      <c r="A22" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="C22" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="D22" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" ht="28" spans="1:6">
-      <c r="A23" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="A23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="C23" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="D23" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" ht="28" spans="1:6">
-      <c r="A24" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="A24" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="C24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" ht="42" spans="1:6">
-      <c r="A25" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="29" t="s">
+      <c r="D24" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="E24" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" ht="28" spans="1:6">
+      <c r="A25" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="C25" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="D25" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="9"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="33" t="s">
+      <c r="A30" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="34" t="s">
-        <v>19</v>
+      <c r="C30" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1" spans="1:6">
-      <c r="A31" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>85</v>
       </c>
+      <c r="D31" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" ht="56" spans="1:6">
-      <c r="A32" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="14" t="s">
+      <c r="A32" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>89</v>
       </c>
+      <c r="D32" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="33" ht="28" spans="1:5">
-      <c r="A33" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="14" t="s">
+      <c r="A33" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="C33" s="12" t="s">
         <v>93</v>
       </c>
+      <c r="D33" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="34" ht="28" spans="1:5">
-      <c r="A34" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="14" t="s">
+      <c r="A34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="C34" s="12" t="s">
         <v>97</v>
       </c>
+      <c r="D34" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="35" ht="28" spans="1:5">
-      <c r="A35" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="A35" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="C35" s="12" t="s">
         <v>101</v>
       </c>
+      <c r="D35" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="36" ht="28" spans="1:5">
-      <c r="A36" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="A36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="C36" s="12" t="s">
         <v>105</v>
       </c>
+      <c r="D36" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="37" ht="42" spans="1:5">
-      <c r="A37" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="18" t="s">
+      <c r="A37" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="C37" s="16" t="s">
         <v>109</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" ht="42" spans="1:5">
-      <c r="A43" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="37" t="s">
+      <c r="A43" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="B43" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="C43" s="35" t="s">
         <v>117</v>
       </c>
+      <c r="D43" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="44" ht="28" spans="1:5">
-      <c r="A44" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="14" t="s">
+      <c r="A44" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="C44" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="D44" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="45" ht="28" spans="1:5">
-      <c r="A45" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" s="14" t="s">
+      <c r="A45" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="C45" s="12" t="s">
         <v>125</v>
       </c>
+      <c r="D45" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="46" ht="28" spans="1:5">
-      <c r="A46" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46" s="14" t="s">
+      <c r="A46" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="C46" s="12" t="s">
         <v>129</v>
       </c>
+      <c r="D46" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="47" ht="28" spans="1:5">
-      <c r="A47" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D47" s="14" t="s">
+      <c r="A47" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="C47" s="12" t="s">
         <v>133</v>
       </c>
+      <c r="D47" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="48" ht="28" spans="1:5">
-      <c r="A48" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D48" s="14" t="s">
+      <c r="A48" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="C48" s="12" t="s">
         <v>137</v>
       </c>
+      <c r="D48" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="49" ht="28" spans="1:5">
-      <c r="A49" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" s="18" t="s">
+      <c r="A49" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="C49" s="16" t="s">
         <v>141</v>
       </c>
+      <c r="D49" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="50" ht="28" spans="1:5">
-      <c r="A50" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="B50" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C50" s="41" t="s">
+      <c r="A50" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="41" t="s">
+      <c r="B50" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="E50" s="42" t="s">
+      <c r="C50" s="39" t="s">
         <v>146</v>
       </c>
+      <c r="D50" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="51" ht="28" spans="1:5">
-      <c r="A51" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="26" t="s">
+      <c r="A51" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="E51" s="27" t="s">
+      <c r="C51" s="24" t="s">
         <v>150</v>
       </c>
+      <c r="D51" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="52" ht="28" spans="1:5">
-      <c r="A52" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52" s="26" t="s">
+      <c r="A52" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="27" t="s">
+      <c r="C52" s="24" t="s">
         <v>154</v>
       </c>
+      <c r="D52" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="53" ht="28" spans="1:5">
-      <c r="A53" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="D53" s="26" t="s">
+      <c r="A53" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E53" s="27" t="s">
+      <c r="C53" s="24" t="s">
         <v>158</v>
       </c>
+      <c r="D53" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="54" ht="28" spans="1:5">
-      <c r="A54" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C54" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="D54" s="26" t="s">
+      <c r="A54" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E54" s="27" t="s">
+      <c r="C54" s="24" t="s">
         <v>162</v>
       </c>
+      <c r="D54" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="55" ht="28" spans="1:5">
-      <c r="A55" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="26" t="s">
+      <c r="A55" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="27" t="s">
+      <c r="C55" s="24" t="s">
         <v>166</v>
       </c>
+      <c r="D55" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="56" ht="28" spans="1:5">
-      <c r="A56" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="B56" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D56" s="30" t="s">
+      <c r="A56" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="C56" s="28" t="s">
         <v>170</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:5">
       <c r="A59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>172</v>
-      </c>
-      <c r="B60"/>
+        <v>174</v>
+      </c>
       <c r="C60" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" ht="28" spans="1:5">
-      <c r="A61" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B61" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="37" t="s">
+      <c r="A61" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="B61" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="E61" s="38" t="s">
+      <c r="C61" s="35" t="s">
         <v>178</v>
       </c>
+      <c r="D61" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="62" ht="28" spans="1:5">
-      <c r="A62" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D62" s="14" t="s">
+      <c r="A62" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="C62" s="12" t="s">
         <v>182</v>
       </c>
+      <c r="D62" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="63" ht="28" spans="1:5">
-      <c r="A63" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D63" s="14" t="s">
+      <c r="A63" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="C63" s="12" t="s">
         <v>186</v>
       </c>
+      <c r="D63" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="64" ht="42" spans="1:5">
-      <c r="A64" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="14" t="s">
+      <c r="A64" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="C64" s="12" t="s">
         <v>190</v>
       </c>
+      <c r="D64" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="65" ht="28" spans="1:5">
-      <c r="A65" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D65" s="14" t="s">
+      <c r="A65" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="C65" s="12" t="s">
         <v>194</v>
       </c>
+      <c r="D65" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="66" ht="28" spans="1:5">
-      <c r="A66" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" s="14" t="s">
+      <c r="A66" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="C66" s="12" t="s">
         <v>198</v>
       </c>
+      <c r="D66" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="67" ht="28" spans="1:5">
-      <c r="A67" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" s="18" t="s">
+      <c r="A67" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="C67" s="16" t="s">
         <v>202</v>
       </c>
+      <c r="D67" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="68" ht="42" spans="1:5">
-      <c r="A68" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="B68" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="C68" s="41" t="s">
+      <c r="A68" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="D68" s="41" t="s">
+      <c r="B68" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="E68" s="42" t="s">
+      <c r="C68" s="39" t="s">
         <v>207</v>
       </c>
+      <c r="D68" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="E68" s="40" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="69" ht="28" spans="1:5">
-      <c r="A69" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B69" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="C69" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D69" s="26" t="s">
+      <c r="A69" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B69" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="E69" s="27" t="s">
+      <c r="C69" s="24" t="s">
         <v>211</v>
       </c>
+      <c r="D69" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="70" ht="28" spans="1:5">
-      <c r="A70" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B70" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C70" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="D70" s="26" t="s">
+      <c r="A70" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="E70" s="27" t="s">
+      <c r="C70" s="24" t="s">
         <v>215</v>
       </c>
+      <c r="D70" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="71" ht="28" spans="1:5">
-      <c r="A71" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B71" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="C71" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="D71" s="26" t="s">
+      <c r="A71" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="E71" s="27" t="s">
+      <c r="C71" s="24" t="s">
         <v>219</v>
       </c>
+      <c r="D71" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="72" ht="28" spans="1:5">
-      <c r="A72" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="D72" s="26" t="s">
+      <c r="A72" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="E72" s="27" t="s">
+      <c r="C72" s="24" t="s">
         <v>223</v>
       </c>
+      <c r="D72" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="73" ht="28" spans="1:5">
-      <c r="A73" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C73" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="D73" s="26" t="s">
+      <c r="A73" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B73" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="E73" s="27" t="s">
+      <c r="C73" s="24" t="s">
         <v>227</v>
       </c>
+      <c r="D73" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="25" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="74" ht="28" spans="1:5">
-      <c r="A74" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B74" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="C74" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="D74" s="30" t="s">
+      <c r="A74" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="E74" s="31" t="s">
+      <c r="C74" s="28" t="s">
         <v>231</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E74" s="29" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" ht="42" spans="1:5">
       <c r="A79" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B79" t="s">
-        <v>234</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="D79" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="C79" s="9" t="s">
         <v>237</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="80" ht="28" spans="1:5">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="C80" s="9" t="s">
         <v>241</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="81" ht="42" spans="1:5">
       <c r="A81" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B81" t="s">
-        <v>242</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D81" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="C81" s="9" t="s">
         <v>245</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="82" ht="28" spans="1:5">
       <c r="A82" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B82" t="s">
-        <v>246</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D82" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="C82" s="9" t="s">
         <v>249</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="83" ht="28" spans="1:5">
       <c r="A83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B83" t="s">
-        <v>250</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="D83" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="C83" s="9" t="s">
         <v>253</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="84" ht="28" spans="1:5">
       <c r="A84" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D84" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="C84" s="9" t="s">
         <v>257</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="85" ht="28" spans="1:5">
       <c r="A85" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B85" t="s">
-        <v>258</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D85" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="C85" s="9" t="s">
         <v>261</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="86" ht="28" spans="1:5">
       <c r="A86" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s">
-        <v>263</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D86" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="C86" s="9" t="s">
         <v>266</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="87" ht="28" spans="1:5">
       <c r="A87" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B87" t="s">
-        <v>267</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D87" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="C87" s="9" t="s">
         <v>270</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="88" ht="28" spans="1:5">
       <c r="A88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B88" t="s">
-        <v>271</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D88" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="C88" s="9" t="s">
         <v>274</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="89" ht="28" spans="1:5">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>275</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="D89" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="C89" s="9" t="s">
         <v>278</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92" ht="28" spans="1:5">
       <c r="A92" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="D92" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="C92" s="9" t="s">
         <v>284</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B93" t="s">
-        <v>285</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D93" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="C93" s="9" t="s">
         <v>288</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="94" ht="28" spans="1:5">
       <c r="A94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B94" t="s">
-        <v>289</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D94" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="C94" s="9" t="s">
         <v>292</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s">
-        <v>293</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D95" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="C95" s="9" t="s">
         <v>296</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s">
-        <v>297</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D96" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="C96" s="9" t="s">
         <v>300</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="D97" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="C97" s="9" t="s">
         <v>304</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
